--- a/SCHOOL_RESULT_SYSTEM/CLASS_DATA/FOUR.xlsx
+++ b/SCHOOL_RESULT_SYSTEM/CLASS_DATA/FOUR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SYTEM\SCHOOL_RESULT_SYSTEM\CLASS_DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9817BC84-A340-4205-9B93-4730483EF534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428BDE24-0516-40D5-B831-311BBE66BDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{CED4DE98-B28C-4730-9DA8-A368C1B97B73}"/>
+    <workbookView xWindow="3045" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{CED4DE98-B28C-4730-9DA8-A368C1B97B73}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>RollNo</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Science_Max</t>
+  </si>
+  <si>
+    <t>Ali</t>
   </si>
 </sst>
 </file>
@@ -604,20 +607,41 @@
       <c r="A3" s="3">
         <v>2</v>
       </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3">
+        <v>50</v>
+      </c>
       <c r="D3" s="3">
         <v>75</v>
       </c>
+      <c r="E3" s="3">
+        <v>55</v>
+      </c>
       <c r="F3" s="3">
         <v>75</v>
       </c>
+      <c r="G3" s="3">
+        <v>44</v>
+      </c>
       <c r="H3" s="3">
         <v>50</v>
       </c>
+      <c r="I3" s="3">
+        <v>24</v>
+      </c>
       <c r="J3" s="3">
         <v>25</v>
       </c>
+      <c r="K3" s="3">
+        <v>40</v>
+      </c>
       <c r="L3" s="3">
         <v>50</v>
+      </c>
+      <c r="M3" s="3">
+        <v>48</v>
       </c>
       <c r="N3" s="3">
         <v>50</v>
